--- a/output/tables/df_ports_TO_analysis_stats.xlsx
+++ b/output/tables/df_ports_TO_analysis_stats.xlsx
@@ -606,25 +606,25 @@
         <v>0.5716117326406065</v>
       </c>
       <c r="K2" t="n">
-        <v>4.310493346128086</v>
+        <v>4.310493346128085</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3662117123940137</v>
+        <v>-0.3662117123940134</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.694577544741063</v>
+        <v>-1.694577544741061</v>
       </c>
       <c r="N2" t="n">
-        <v>0.480341063150309</v>
+        <v>0.4803410631503091</v>
       </c>
       <c r="O2" t="n">
-        <v>2.43850949031147</v>
+        <v>2.438509490311469</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2695635190025602</v>
+        <v>0.2695635190025603</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.925777117053082</v>
+        <v>1.925777117053081</v>
       </c>
       <c r="R2" t="n">
         <v>0.08790055513475636</v>
@@ -708,28 +708,28 @@
         <v>4.568060027703954</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5613317167743772</v>
+        <v>0.5613317167743773</v>
       </c>
       <c r="K3" t="n">
         <v>4.275334925300991</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3627123420988964</v>
+        <v>-0.3627123420988959</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.677727347189434</v>
+        <v>-1.677727347189431</v>
       </c>
       <c r="N3" t="n">
         <v>0.4834529193918959</v>
       </c>
       <c r="O3" t="n">
-        <v>2.473070960299703</v>
+        <v>2.473070960299702</v>
       </c>
       <c r="P3" t="n">
         <v>0.2771978347587338</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.99923805665807</v>
+        <v>1.999238056658069</v>
       </c>
       <c r="R3" t="n">
         <v>0.08714729517222597</v>
@@ -813,28 +813,28 @@
         <v>3.735415457083926</v>
       </c>
       <c r="J4" t="n">
-        <v>0.559698079310017</v>
+        <v>0.5596980793100171</v>
       </c>
       <c r="K4" t="n">
-        <v>4.268303093072794</v>
+        <v>4.268303093072793</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3568452116498622</v>
+        <v>-0.3568452116498619</v>
       </c>
       <c r="M4" t="n">
         <v>-1.644569526407188</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4761066850989953</v>
+        <v>0.4761066850989952</v>
       </c>
       <c r="O4" t="n">
-        <v>2.423653261626804</v>
+        <v>2.423653261626803</v>
       </c>
       <c r="P4" t="n">
         <v>0.2689608697795874</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.962052147864041</v>
+        <v>1.96205214786404</v>
       </c>
       <c r="R4" t="n">
         <v>0.08537423012844558</v>
@@ -912,34 +912,34 @@
         <v>2.788246106422154</v>
       </c>
       <c r="H5" t="n">
-        <v>0.410474402027949</v>
+        <v>0.4104744020279492</v>
       </c>
       <c r="I5" t="n">
         <v>6.39908743364318</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2597929243757444</v>
+        <v>0.259792924375744</v>
       </c>
       <c r="K5" t="n">
-        <v>2.051279231664066</v>
+        <v>2.051279231664063</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2397165948535649</v>
+        <v>-0.2397165948535646</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.379649752901663</v>
+        <v>-1.379649752901662</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6143611757622188</v>
+        <v>0.6143611757622193</v>
       </c>
       <c r="O5" t="n">
-        <v>3.134869624078841</v>
+        <v>3.134869624078842</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.211089175119606</v>
+        <v>-0.2110891751196062</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.371388932693089</v>
+        <v>-1.37138893269309</v>
       </c>
       <c r="R5" t="n">
         <v>0.1000752787213028</v>
@@ -1017,31 +1017,31 @@
         <v>2.788246106422154</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3430319789277412</v>
+        <v>0.3430319789277413</v>
       </c>
       <c r="I6" t="n">
         <v>5.357176871475987</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2523820043373254</v>
+        <v>0.2523820043373252</v>
       </c>
       <c r="K6" t="n">
-        <v>2.002319985200463</v>
+        <v>2.00231998520046</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2274331188817208</v>
+        <v>-0.2274331188817206</v>
       </c>
       <c r="M6" t="n">
         <v>-1.30345049497981</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6130410031260654</v>
+        <v>0.6130410031260659</v>
       </c>
       <c r="O6" t="n">
-        <v>3.145480864401485</v>
+        <v>3.145480864401486</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2040526458643821</v>
+        <v>-0.2040526458643822</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.345371442690972</v>
@@ -1128,31 +1128,31 @@
         <v>4.557070222017861</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2507483668729673</v>
+        <v>0.250748366872967</v>
       </c>
       <c r="K7" t="n">
-        <v>1.995773882928849</v>
+        <v>1.995773882928846</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2215659884326877</v>
+        <v>-0.2215659884326875</v>
       </c>
       <c r="M7" t="n">
         <v>-1.267825474009309</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6056947688331631</v>
+        <v>0.6056947688331638</v>
       </c>
       <c r="O7" t="n">
-        <v>3.126813700235314</v>
+        <v>3.126813700235317</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2122896108435292</v>
+        <v>-0.2122896108435295</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.423040140734475</v>
+        <v>-1.423040140734477</v>
       </c>
       <c r="R7" t="n">
-        <v>0.09652765302205124</v>
+        <v>0.09652765302205102</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
